--- a/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
+++ b/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-03T20:30:38+00:00</t>
+    <t>2026-05-03T21:28:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
+++ b/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-03T21:28:00+00:00</t>
+    <t>2026-05-04T06:23:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
+++ b/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T06:23:23+00:00</t>
+    <t>2026-05-04T06:44:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
+++ b/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T06:44:52+00:00</t>
+    <t>2026-05-04T07:06:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
+++ b/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:06:34+00:00</t>
+    <t>2026-05-04T07:30:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
+++ b/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:30:32+00:00</t>
+    <t>2026-05-04T07:50:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
+++ b/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:50:36+00:00</t>
+    <t>2026-05-04T08:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
+++ b/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:11:13+00:00</t>
+    <t>2026-05-04T08:32:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
+++ b/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:32:13+00:00</t>
+    <t>2026-05-04T09:30:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
+++ b/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T09:30:07+00:00</t>
+    <t>2026-05-04T09:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
+++ b/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T09:51:52+00:00</t>
+    <t>2026-05-04T11:25:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
+++ b/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T11:25:12+00:00</t>
+    <t>2026-05-04T11:47:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
+++ b/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T11:47:21+00:00</t>
+    <t>2026-05-04T12:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
+++ b/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T12:11:06+00:00</t>
+    <t>2026-05-04T13:22:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
+++ b/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:22:07+00:00</t>
+    <t>2026-05-04T13:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
+++ b/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:47:49+00:00</t>
+    <t>2026-05-04T14:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
+++ b/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:15:24+00:00</t>
+    <t>2026-05-04T14:55:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
+++ b/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:55:41+00:00</t>
+    <t>2026-05-04T15:18:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
+++ b/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T15:18:17+00:00</t>
+    <t>2026-05-04T15:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
+++ b/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T18:43:40+00:00</t>
+    <t>2026-05-12T08:39:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
+++ b/ci-build/StructureDefinition-senologie-tumorlokalisation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$29</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="249">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T08:39:42+00:00</t>
+    <t>2026-05-12T14:42:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -235,6 +235,12 @@
   </si>
   <si>
     <t>Constraint(s)</t>
+  </si>
+  <si>
+    <t>Mapping: BIH LM Senologie</t>
+  </si>
+  <si>
+    <t>Mapping: LM-Element: Tumorlokalisation</t>
   </si>
   <si>
     <t xml:space="preserve">anatomical location
@@ -1104,7 +1110,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ29"/>
+  <dimension ref="A1:AL29"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.88671875" customWidth="true" bestFit="true"/>
@@ -1142,6 +1148,8 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
+    <col min="37" max="37" width="25.35546875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="37.46875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1253,6 +1261,12 @@
       <c r="AJ1" t="s" s="1">
         <v>72</v>
       </c>
+      <c r="AK1" t="s" s="1">
+        <v>73</v>
+      </c>
+      <c r="AL1" t="s" s="1">
+        <v>74</v>
+      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -1263,14 +1277,14 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -1282,13 +1296,13 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -1342,24 +1356,30 @@
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
+      </c>
+      <c r="AK2" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1367,31 +1387,31 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I3" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1441,27 +1461,33 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL3" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1469,28 +1495,28 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1541,27 +1567,33 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
+      </c>
+      <c r="AK4" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL4" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1569,10 +1601,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
@@ -1584,13 +1616,13 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1641,38 +1673,44 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK5" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL5" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -1684,16 +1722,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1731,39 +1769,45 @@
         <v>20</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
+      </c>
+      <c r="AK6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL6" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1771,10 +1815,10 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -1783,19 +1827,19 @@
         <v>20</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -1845,27 +1889,33 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1873,10 +1923,10 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -1885,19 +1935,19 @@
         <v>20</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1947,27 +1997,33 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
+      </c>
+      <c r="AK8" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL8" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1975,31 +2031,31 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2049,27 +2105,33 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
+      </c>
+      <c r="AK9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL9" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2077,31 +2139,31 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2151,27 +2213,33 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
+      </c>
+      <c r="AK10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL10" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2179,10 +2247,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
@@ -2191,19 +2259,19 @@
         <v>20</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2229,13 +2297,13 @@
         <v>20</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>20</v>
@@ -2253,27 +2321,33 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
+      </c>
+      <c r="AK11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2281,10 +2355,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -2293,19 +2367,19 @@
         <v>20</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2331,13 +2405,13 @@
         <v>20</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>20</v>
@@ -2355,27 +2429,33 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
+      </c>
+      <c r="AK12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2383,31 +2463,31 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2457,27 +2537,33 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2485,10 +2571,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -2500,16 +2586,16 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2535,13 +2621,13 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
@@ -2559,38 +2645,44 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -2602,16 +2694,16 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2661,38 +2753,44 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
+      </c>
+      <c r="AK15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -2704,16 +2802,16 @@
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -2763,38 +2861,44 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -2806,16 +2910,16 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2853,74 +2957,80 @@
         <v>20</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -2957,39 +3067,45 @@
         <v>20</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
+      </c>
+      <c r="AK18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2997,10 +3113,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -3009,16 +3125,16 @@
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3069,27 +3185,33 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
+      </c>
+      <c r="AK19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3097,105 +3219,111 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="P20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q20" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="R20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF20" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="M20" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="P20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q20" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="R20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>191</v>
-      </c>
       <c r="AG20" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3203,31 +3331,31 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3253,13 +3381,13 @@
         <v>20</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>20</v>
@@ -3277,27 +3405,33 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3305,31 +3439,31 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3355,13 +3489,13 @@
         <v>20</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>20</v>
@@ -3379,27 +3513,33 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
+      </c>
+      <c r="AK22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3407,13 +3547,13 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>20</v>
@@ -3422,16 +3562,16 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3457,65 +3597,71 @@
         <v>20</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>20</v>
@@ -3524,16 +3670,16 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3559,13 +3705,13 @@
         <v>20</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>20</v>
@@ -3583,43 +3729,49 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>20</v>
@@ -3628,16 +3780,16 @@
         <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -3663,13 +3815,13 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -3687,43 +3839,49 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>20</v>
@@ -3732,16 +3890,16 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -3767,13 +3925,13 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -3791,27 +3949,33 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3819,31 +3983,31 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -3893,27 +4057,33 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3921,10 +4091,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -3936,16 +4106,16 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -3995,27 +4165,33 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4023,31 +4199,31 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4097,23 +4273,29 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ29">
+  <autoFilter ref="A1:AL29">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
